--- a/data/k-props/2026-08-10.xlsx
+++ b/data/k-props/2026-08-10.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="84">
   <si>
     <t>date</t>
   </si>
@@ -181,13 +181,19 @@
     <t>Bryce Elder</t>
   </si>
   <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Minnesota Twins</t>
+  </si>
+  <si>
     <t>Trevor Rogers</t>
   </si>
   <si>
-    <t>Baltimore Orioles @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>posted</t>
   </si>
   <si>
     <t>Andrew Painter</t>
@@ -199,27 +205,27 @@
     <t>Hunter Dobbins</t>
   </si>
   <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Los Angeles Angels</t>
+  </si>
+  <si>
     <t>MacKenzie Gore</t>
   </si>
   <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
+    <t>Michael Soroka</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Arizona Diamondbacks</t>
   </si>
   <si>
     <t>Gabriel Hughes</t>
   </si>
   <si>
-    <t>Colorado Rockies @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Michael Soroka</t>
-  </si>
-  <si>
     <t>Freddy Peralta</t>
   </si>
   <si>
@@ -247,13 +253,16 @@
     <t>Houston Astros @ San Francisco Giants</t>
   </si>
   <si>
+    <t>Hayden Wesneski</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Dodgers</t>
+  </si>
+  <si>
     <t>Noah Cameron</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Tarik Skubal</t>
   </si>
 </sst>
 </file>
@@ -634,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ20"/>
+  <dimension ref="A1:AQ21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="43" width="16" customWidth="1"/>
@@ -778,8 +787,17 @@
       <c r="B2" t="s">
         <v>44</v>
       </c>
+      <c r="C2">
+        <v>4.5</v>
+      </c>
+      <c r="D2">
+        <v>-111</v>
+      </c>
+      <c r="E2">
+        <v>-102</v>
+      </c>
       <c r="F2">
-        <v>4.17</v>
+        <v>4.37</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -812,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T2">
         <v>0.219</v>
@@ -839,7 +857,7 @@
         <v>4.04</v>
       </c>
       <c r="AB2">
-        <v>0.9278</v>
+        <v>0.9293</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
@@ -857,7 +875,7 @@
         <v>0.1891</v>
       </c>
       <c r="AH2">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI2">
         <v>0.9789</v>
@@ -872,7 +890,7 @@
         <v>50</v>
       </c>
       <c r="AM2">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
@@ -882,8 +900,17 @@
       <c r="B3" t="s">
         <v>51</v>
       </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+      <c r="D3">
+        <v>120</v>
+      </c>
+      <c r="E3">
+        <v>-133</v>
+      </c>
       <c r="F3">
-        <v>3.76</v>
+        <v>3.97</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -892,7 +919,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -916,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T3">
         <v>0.2081</v>
@@ -943,7 +970,7 @@
         <v>4.33</v>
       </c>
       <c r="AB3">
-        <v>0.8568</v>
+        <v>0.8582</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
@@ -961,7 +988,7 @@
         <v>0.2188</v>
       </c>
       <c r="AH3">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI3">
         <v>0.9969</v>
@@ -976,7 +1003,7 @@
         <v>50</v>
       </c>
       <c r="AM3">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
@@ -986,8 +1013,17 @@
       <c r="B4" t="s">
         <v>52</v>
       </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+      <c r="D4">
+        <v>105</v>
+      </c>
+      <c r="E4">
+        <v>-119</v>
+      </c>
       <c r="F4">
-        <v>6.75</v>
+        <v>6.51</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -996,7 +1032,7 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
       <c r="L4" t="s">
         <v>53</v>
@@ -1020,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>0.2884</v>
@@ -1047,7 +1083,7 @@
         <v>4.29</v>
       </c>
       <c r="AB4">
-        <v>1.0919</v>
+        <v>1.0937</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
@@ -1065,7 +1101,7 @@
         <v>0.2176</v>
       </c>
       <c r="AH4">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI4">
         <v>1.0158</v>
@@ -1080,7 +1116,7 @@
         <v>50</v>
       </c>
       <c r="AM4">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
@@ -1090,8 +1126,17 @@
       <c r="B5" t="s">
         <v>55</v>
       </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>-113</v>
+      </c>
       <c r="F5">
-        <v>5.06</v>
+        <v>5.26</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1124,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>0.1966</v>
@@ -1151,7 +1196,7 @@
         <v>4.18</v>
       </c>
       <c r="AB5">
-        <v>1.1478</v>
+        <v>1.1497</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
@@ -1169,7 +1214,7 @@
         <v>0.2248</v>
       </c>
       <c r="AH5">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI5">
         <v>0.9914</v>
@@ -1184,7 +1229,7 @@
         <v>50</v>
       </c>
       <c r="AM5">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
@@ -1194,8 +1239,17 @@
       <c r="B6" t="s">
         <v>56</v>
       </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+      <c r="D6">
+        <v>116</v>
+      </c>
+      <c r="E6">
+        <v>-134</v>
+      </c>
       <c r="F6">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1204,7 +1258,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
@@ -1219,7 +1273,7 @@
         <v>48</v>
       </c>
       <c r="P6">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1228,55 +1282,55 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>0.2025</v>
+        <v>0.2326</v>
       </c>
       <c r="U6">
-        <v>0.2261</v>
+        <v>0.2167</v>
       </c>
       <c r="V6">
         <v>5</v>
       </c>
       <c r="W6">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="X6">
-        <v>0.264</v>
+        <v>0.1869</v>
       </c>
       <c r="Y6">
-        <v>0.385</v>
+        <v>0.349</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="AB6">
-        <v>0.8907</v>
+        <v>1.1299</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
       </c>
       <c r="AD6">
-        <v>0.1932</v>
+        <v>0.2447</v>
       </c>
       <c r="AE6">
-        <v>0.193</v>
+        <v>0.2682</v>
       </c>
       <c r="AF6">
         <v>9</v>
       </c>
       <c r="AG6">
-        <v>0.2209</v>
+        <v>0.2379</v>
       </c>
       <c r="AH6">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI6">
-        <v>0.9704</v>
+        <v>1.0071</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
@@ -1288,7 +1342,7 @@
         <v>50</v>
       </c>
       <c r="AM6">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
@@ -1298,8 +1352,17 @@
       <c r="B7" t="s">
         <v>58</v>
       </c>
+      <c r="C7">
+        <v>4.5</v>
+      </c>
+      <c r="D7">
+        <v>-136</v>
+      </c>
+      <c r="E7">
+        <v>119</v>
+      </c>
       <c r="F7">
-        <v>5.09</v>
+        <v>3.99</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1308,7 +1371,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>5.29</v>
+        <v>3.99</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -1323,7 +1386,7 @@
         <v>48</v>
       </c>
       <c r="P7">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1332,67 +1395,67 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>0.2326</v>
+        <v>0.2025</v>
       </c>
       <c r="U7">
-        <v>0.2167</v>
+        <v>0.2261</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="X7">
-        <v>0.1869</v>
+        <v>0.264</v>
       </c>
       <c r="Y7">
-        <v>0.349</v>
+        <v>0.385</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="AB7">
-        <v>1.1281</v>
+        <v>0.8601</v>
       </c>
       <c r="AC7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AD7">
-        <v>0.2447</v>
+        <v>0.1862</v>
       </c>
       <c r="AE7">
-        <v>0.2682</v>
+        <v>0.1904</v>
       </c>
       <c r="AF7">
         <v>9</v>
       </c>
       <c r="AG7">
-        <v>0.2379</v>
+        <v>0.2209</v>
       </c>
       <c r="AH7">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI7">
-        <v>1.0071</v>
+        <v>0.8897</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM7">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
@@ -1400,10 +1463,19 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+      <c r="C8">
+        <v>3.5</v>
+      </c>
+      <c r="D8">
+        <v>110</v>
+      </c>
+      <c r="E8">
+        <v>-135</v>
       </c>
       <c r="F8">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1418,7 +1490,7 @@
         <v>46</v>
       </c>
       <c r="M8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N8">
         <v>823018</v>
@@ -1436,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T8">
         <v>0.1858</v>
@@ -1463,7 +1535,7 @@
         <v>4.52</v>
       </c>
       <c r="AB8">
-        <v>0.9534</v>
+        <v>0.955</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
@@ -1481,7 +1553,7 @@
         <v>0.212</v>
       </c>
       <c r="AH8">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI8">
         <v>0.9551</v>
@@ -1496,7 +1568,7 @@
         <v>50</v>
       </c>
       <c r="AM8">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
@@ -1504,10 +1576,19 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="C9">
+        <v>3.5</v>
+      </c>
+      <c r="D9">
+        <v>112</v>
+      </c>
+      <c r="E9">
+        <v>-135</v>
       </c>
       <c r="F9">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1522,7 +1603,7 @@
         <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N9">
         <v>823018</v>
@@ -1540,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>0.213</v>
@@ -1567,7 +1648,7 @@
         <v>4.22</v>
       </c>
       <c r="AB9">
-        <v>0.848</v>
+        <v>0.8494</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
@@ -1585,7 +1666,7 @@
         <v>0.2262</v>
       </c>
       <c r="AH9">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI9">
         <v>0.9677</v>
@@ -1600,7 +1681,7 @@
         <v>50</v>
       </c>
       <c r="AM9">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
@@ -1608,10 +1689,19 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="C10">
+        <v>6.5</v>
+      </c>
+      <c r="D10">
+        <v>-132</v>
+      </c>
+      <c r="E10">
+        <v>117</v>
       </c>
       <c r="F10">
-        <v>7.62</v>
+        <v>7.39</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1620,13 +1710,13 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>7.62</v>
+        <v>7.39</v>
       </c>
       <c r="L10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N10">
         <v>823998</v>
@@ -1635,7 +1725,7 @@
         <v>48</v>
       </c>
       <c r="P10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1644,55 +1734,55 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>0.2559</v>
+        <v>0.283</v>
       </c>
       <c r="U10">
-        <v>0.2554</v>
+        <v>0.3007</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="X10">
-        <v>0.2544</v>
+        <v>0.3367</v>
       </c>
       <c r="Y10">
-        <v>0.363</v>
+        <v>0.329</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="AB10">
-        <v>1.2593</v>
+        <v>1.0432</v>
       </c>
       <c r="AC10" t="s">
         <v>49</v>
       </c>
       <c r="AD10">
-        <v>0.2731</v>
+        <v>0.2259</v>
       </c>
       <c r="AE10">
-        <v>0.2647</v>
+        <v>0.2363</v>
       </c>
       <c r="AF10">
         <v>9</v>
       </c>
       <c r="AG10">
-        <v>0.2606</v>
+        <v>0.2496</v>
       </c>
       <c r="AH10">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI10">
-        <v>1.0392</v>
+        <v>1.0227</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
@@ -1712,25 +1802,34 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+      <c r="D11">
+        <v>106</v>
+      </c>
+      <c r="E11">
+        <v>-115</v>
+      </c>
+      <c r="F11">
+        <v>7.63</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11">
+        <v>7.63</v>
+      </c>
+      <c r="L11" t="s">
         <v>65</v>
       </c>
-      <c r="F11">
-        <v>7.38</v>
-      </c>
-      <c r="H11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11">
-        <v>7.38</v>
-      </c>
-      <c r="L11" t="s">
-        <v>63</v>
-      </c>
       <c r="M11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N11">
         <v>823998</v>
@@ -1739,7 +1838,7 @@
         <v>48</v>
       </c>
       <c r="P11">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
@@ -1748,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>0.283</v>
+        <v>0.2559</v>
       </c>
       <c r="U11">
-        <v>0.3007</v>
+        <v>0.2554</v>
       </c>
       <c r="V11">
         <v>5</v>
       </c>
       <c r="W11">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="X11">
-        <v>0.3367</v>
+        <v>0.2544</v>
       </c>
       <c r="Y11">
-        <v>0.329</v>
+        <v>0.363</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>4.11</v>
+        <v>4.25</v>
       </c>
       <c r="AB11">
-        <v>1.0416</v>
+        <v>1.2614</v>
       </c>
       <c r="AC11" t="s">
         <v>49</v>
       </c>
       <c r="AD11">
-        <v>0.2259</v>
+        <v>0.2731</v>
       </c>
       <c r="AE11">
-        <v>0.2363</v>
+        <v>0.2647</v>
       </c>
       <c r="AF11">
         <v>9</v>
       </c>
       <c r="AG11">
-        <v>0.2496</v>
+        <v>0.2606</v>
       </c>
       <c r="AH11">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI11">
-        <v>1.0227</v>
+        <v>1.0392</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
@@ -1816,10 +1915,19 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12">
+        <v>116</v>
+      </c>
+      <c r="E12">
+        <v>-134</v>
       </c>
       <c r="F12">
-        <v>3.81</v>
+        <v>5.37</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1828,13 +1936,13 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>4.01</v>
+        <v>5.37</v>
       </c>
       <c r="L12" t="s">
         <v>46</v>
       </c>
       <c r="M12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N12">
         <v>825048</v>
@@ -1843,7 +1951,7 @@
         <v>48</v>
       </c>
       <c r="P12">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1852,55 +1960,55 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>0.2314</v>
+        <v>0.2372</v>
       </c>
       <c r="U12">
-        <v>0.2364</v>
+        <v>0.2315</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="X12">
-        <v>0.2455</v>
+        <v>0.22</v>
       </c>
       <c r="Y12">
-        <v>0.355</v>
+        <v>0.333</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="AB12">
-        <v>0.8516</v>
+        <v>1.0432</v>
       </c>
       <c r="AC12" t="s">
         <v>49</v>
       </c>
       <c r="AD12">
-        <v>0.1847</v>
+        <v>0.2259</v>
       </c>
       <c r="AE12">
-        <v>0.183</v>
+        <v>0.2243</v>
       </c>
       <c r="AF12">
         <v>9</v>
       </c>
       <c r="AG12">
-        <v>0.2012</v>
+        <v>0.2169</v>
       </c>
       <c r="AH12">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI12">
-        <v>0.9161</v>
+        <v>1.002</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
@@ -1912,7 +2020,7 @@
         <v>50</v>
       </c>
       <c r="AM12">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
@@ -1920,10 +2028,19 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="C13">
+        <v>3.5</v>
+      </c>
+      <c r="D13">
+        <v>-126</v>
+      </c>
+      <c r="E13">
+        <v>116</v>
       </c>
       <c r="F13">
-        <v>5.16</v>
+        <v>4.02</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -1932,13 +2049,13 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>5.36</v>
+        <v>4.02</v>
       </c>
       <c r="L13" t="s">
         <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N13">
         <v>825048</v>
@@ -1947,7 +2064,7 @@
         <v>48</v>
       </c>
       <c r="P13">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -1956,55 +2073,55 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>0.2372</v>
+        <v>0.2314</v>
       </c>
       <c r="U13">
-        <v>0.2315</v>
+        <v>0.2364</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="X13">
-        <v>0.22</v>
+        <v>0.2455</v>
       </c>
       <c r="Y13">
-        <v>0.333</v>
+        <v>0.355</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="AB13">
-        <v>1.0416</v>
+        <v>0.853</v>
       </c>
       <c r="AC13" t="s">
         <v>49</v>
       </c>
       <c r="AD13">
-        <v>0.2259</v>
+        <v>0.1847</v>
       </c>
       <c r="AE13">
-        <v>0.2243</v>
+        <v>0.183</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
       <c r="AG13">
-        <v>0.2169</v>
+        <v>0.2012</v>
       </c>
       <c r="AH13">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI13">
-        <v>1.002</v>
+        <v>0.9161</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
@@ -2016,7 +2133,7 @@
         <v>50</v>
       </c>
       <c r="AM13">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
@@ -2024,10 +2141,19 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="C14">
+        <v>4.5</v>
+      </c>
+      <c r="D14">
+        <v>-127</v>
+      </c>
+      <c r="E14">
+        <v>112</v>
       </c>
       <c r="F14">
-        <v>6.65</v>
+        <v>6.41</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2036,13 +2162,13 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>6.4</v>
+        <v>6.41</v>
       </c>
       <c r="L14" t="s">
         <v>53</v>
       </c>
       <c r="M14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N14">
         <v>824969</v>
@@ -2060,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>0.2185</v>
@@ -2087,7 +2213,7 @@
         <v>4.53</v>
       </c>
       <c r="AB14">
-        <v>1.2305</v>
+        <v>1.2324</v>
       </c>
       <c r="AC14" t="s">
         <v>49</v>
@@ -2105,7 +2231,7 @@
         <v>0.218</v>
       </c>
       <c r="AH14">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI14">
         <v>1.029</v>
@@ -2120,7 +2246,7 @@
         <v>50</v>
       </c>
       <c r="AM14">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
@@ -2128,10 +2254,19 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="C15">
+        <v>4.5</v>
+      </c>
+      <c r="D15">
+        <v>109</v>
+      </c>
+      <c r="E15">
+        <v>-130</v>
       </c>
       <c r="F15">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2140,19 +2275,19 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N15">
         <v>824969</v>
       </c>
       <c r="O15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P15">
         <v>4.4</v>
@@ -2164,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>0.2029</v>
@@ -2191,7 +2326,7 @@
         <v>4.6</v>
       </c>
       <c r="AB15">
-        <v>0.8341</v>
+        <v>0.8354</v>
       </c>
       <c r="AC15" t="s">
         <v>49</v>
@@ -2209,7 +2344,7 @@
         <v>0.1829</v>
       </c>
       <c r="AH15">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI15">
         <v>0.8918</v>
@@ -2224,7 +2359,7 @@
         <v>50</v>
       </c>
       <c r="AM15">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
@@ -2232,10 +2367,19 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>75</v>
+      </c>
+      <c r="C16">
+        <v>5.5</v>
+      </c>
+      <c r="D16">
+        <v>102</v>
+      </c>
+      <c r="E16">
+        <v>-115</v>
       </c>
       <c r="F16">
-        <v>4.14</v>
+        <v>4.35</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2244,13 +2388,13 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N16">
         <v>823265</v>
@@ -2268,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>0.3229</v>
@@ -2295,7 +2439,7 @@
         <v>3.84</v>
       </c>
       <c r="AB16">
-        <v>0.7127</v>
+        <v>0.7138</v>
       </c>
       <c r="AC16" t="s">
         <v>49</v>
@@ -2313,7 +2457,7 @@
         <v>0.2194</v>
       </c>
       <c r="AH16">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI16">
         <v>0.9922</v>
@@ -2328,7 +2472,7 @@
         <v>50</v>
       </c>
       <c r="AM16">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
@@ -2336,10 +2480,19 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="C17">
+        <v>4.5</v>
+      </c>
+      <c r="D17">
+        <v>-137</v>
+      </c>
+      <c r="E17">
+        <v>117</v>
       </c>
       <c r="F17">
-        <v>4.61</v>
+        <v>4.81</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2354,7 +2507,7 @@
         <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N17">
         <v>823265</v>
@@ -2372,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>0.2369</v>
@@ -2399,7 +2552,7 @@
         <v>4.03</v>
       </c>
       <c r="AB17">
-        <v>1.0714</v>
+        <v>1.0731</v>
       </c>
       <c r="AC17" t="s">
         <v>49</v>
@@ -2417,7 +2570,7 @@
         <v>0.2137</v>
       </c>
       <c r="AH17">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI17">
         <v>0.9959</v>
@@ -2432,7 +2585,7 @@
         <v>50</v>
       </c>
       <c r="AM17">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
@@ -2440,10 +2593,19 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>78</v>
+      </c>
+      <c r="C18">
+        <v>3.5</v>
+      </c>
+      <c r="D18">
+        <v>-130</v>
+      </c>
+      <c r="E18">
+        <v>112</v>
       </c>
       <c r="F18">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2452,13 +2614,13 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="L18" t="s">
         <v>46</v>
       </c>
       <c r="M18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N18">
         <v>823189</v>
@@ -2476,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>0.1884</v>
@@ -2503,7 +2665,7 @@
         <v>4.06</v>
       </c>
       <c r="AB18">
-        <v>0.8407</v>
+        <v>0.842</v>
       </c>
       <c r="AC18" t="s">
         <v>49</v>
@@ -2521,7 +2683,7 @@
         <v>0.2171</v>
       </c>
       <c r="AH18">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI18">
         <v>1.0304</v>
@@ -2536,7 +2698,7 @@
         <v>50</v>
       </c>
       <c r="AM18">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
@@ -2544,10 +2706,16 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19">
-        <v>7.43</v>
+        <v>80</v>
+      </c>
+      <c r="C19">
+        <v>3.5</v>
+      </c>
+      <c r="D19">
+        <v>-154</v>
+      </c>
+      <c r="E19">
+        <v>135</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2555,92 +2723,32 @@
       <c r="J19" t="s">
         <v>45</v>
       </c>
-      <c r="K19">
-        <v>7.43</v>
-      </c>
       <c r="L19" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="M19" t="s">
         <v>79</v>
       </c>
-      <c r="N19">
-        <v>823918</v>
+      <c r="N19" t="s">
+        <v>45</v>
       </c>
       <c r="O19" t="s">
-        <v>48</v>
-      </c>
-      <c r="P19">
-        <v>5.6</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>0</v>
-      </c>
-      <c r="R19" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0.2201</v>
-      </c>
-      <c r="U19">
-        <v>0.2313</v>
-      </c>
-      <c r="V19">
-        <v>5</v>
-      </c>
-      <c r="W19">
-        <v>133</v>
-      </c>
-      <c r="X19">
-        <v>0.2481</v>
-      </c>
-      <c r="Y19">
-        <v>0.399</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>4.26</v>
-      </c>
-      <c r="AB19">
-        <v>1.3694</v>
+        <v>6</v>
       </c>
       <c r="AC19" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD19">
-        <v>0.297</v>
-      </c>
-      <c r="AE19">
-        <v>0.2256</v>
-      </c>
-      <c r="AF19">
-        <v>9</v>
-      </c>
-      <c r="AG19">
-        <v>0.2004</v>
-      </c>
-      <c r="AH19">
-        <v>0.2169</v>
-      </c>
-      <c r="AI19">
-        <v>0.9913</v>
-      </c>
-      <c r="AJ19" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>45</v>
       </c>
       <c r="AK19" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AL19" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
@@ -2648,10 +2756,19 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="C20">
+        <v>7.5</v>
+      </c>
+      <c r="D20">
+        <v>-118</v>
+      </c>
+      <c r="E20">
+        <v>101</v>
       </c>
       <c r="F20">
-        <v>6.58</v>
+        <v>6.34</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2660,13 +2777,13 @@
         <v>45</v>
       </c>
       <c r="K20">
-        <v>6.33</v>
+        <v>6.34</v>
       </c>
       <c r="L20" t="s">
         <v>53</v>
       </c>
       <c r="M20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N20">
         <v>823918</v>
@@ -2684,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>0.3065</v>
@@ -2711,7 +2828,7 @@
         <v>3.88</v>
       </c>
       <c r="AB20">
-        <v>0.9323</v>
+        <v>0.9337</v>
       </c>
       <c r="AC20" t="s">
         <v>49</v>
@@ -2729,7 +2846,7 @@
         <v>0.2091</v>
       </c>
       <c r="AH20">
-        <v>0.2169</v>
+        <v>0.2166</v>
       </c>
       <c r="AI20">
         <v>0.941</v>
@@ -2744,7 +2861,120 @@
         <v>50</v>
       </c>
       <c r="AM20">
-        <v>0.25</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21">
+        <v>4.5</v>
+      </c>
+      <c r="D21">
+        <v>-141</v>
+      </c>
+      <c r="E21">
+        <v>120</v>
+      </c>
+      <c r="F21">
+        <v>7.45</v>
+      </c>
+      <c r="H21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21">
+        <v>7.45</v>
+      </c>
+      <c r="L21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M21" t="s">
+        <v>82</v>
+      </c>
+      <c r="N21">
+        <v>823918</v>
+      </c>
+      <c r="O21" t="s">
+        <v>48</v>
+      </c>
+      <c r="P21">
+        <v>5.6</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>6</v>
+      </c>
+      <c r="T21">
+        <v>0.2201</v>
+      </c>
+      <c r="U21">
+        <v>0.2313</v>
+      </c>
+      <c r="V21">
+        <v>5</v>
+      </c>
+      <c r="W21">
+        <v>133</v>
+      </c>
+      <c r="X21">
+        <v>0.2481</v>
+      </c>
+      <c r="Y21">
+        <v>0.399</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>4.26</v>
+      </c>
+      <c r="AB21">
+        <v>1.3715</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD21">
+        <v>0.297</v>
+      </c>
+      <c r="AE21">
+        <v>0.2256</v>
+      </c>
+      <c r="AF21">
+        <v>9</v>
+      </c>
+      <c r="AG21">
+        <v>0.2004</v>
+      </c>
+      <c r="AH21">
+        <v>0.2166</v>
+      </c>
+      <c r="AI21">
+        <v>0.9913</v>
+      </c>
+      <c r="AJ21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-10.xlsx
+++ b/data/k-props/2026-08-10.xlsx
@@ -160,15 +160,21 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>posted</t>
+  </si>
+  <si>
+    <t>Jameson Taillon</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
   </si>
   <si>
-    <t>Jameson Taillon</t>
-  </si>
-  <si>
     <t>Christian Scott</t>
   </si>
   <si>
@@ -190,12 +196,6 @@
     <t>Trevor Rogers</t>
   </si>
   <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>posted</t>
-  </si>
-  <si>
     <t>Andrew Painter</t>
   </si>
   <si>
@@ -247,13 +247,13 @@
     <t>Casey Mize</t>
   </si>
   <si>
+    <t>Hayden Wesneski</t>
+  </si>
+  <si>
+    <t>Houston Astros @ San Francisco Giants</t>
+  </si>
+  <si>
     <t>Blade Tidwell</t>
-  </si>
-  <si>
-    <t>Houston Astros @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Hayden Wesneski</t>
   </si>
   <si>
     <t>Tarik Skubal</t>
@@ -791,13 +791,13 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-111</v>
+        <v>-119</v>
       </c>
       <c r="E2">
-        <v>-102</v>
+        <v>127</v>
       </c>
       <c r="F2">
-        <v>4.37</v>
+        <v>5.17</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -806,7 +806,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>4.37</v>
+        <v>5.17</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2">
         <v>0.219</v>
@@ -857,16 +857,16 @@
         <v>4.04</v>
       </c>
       <c r="AB2">
-        <v>0.9293</v>
+        <v>1.0606</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
       </c>
       <c r="AD2">
-        <v>0.2012</v>
+        <v>0.2313</v>
       </c>
       <c r="AE2">
-        <v>0.1888</v>
+        <v>0.2159</v>
       </c>
       <c r="AF2">
         <v>9</v>
@@ -875,10 +875,10 @@
         <v>0.1891</v>
       </c>
       <c r="AH2">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI2">
-        <v>0.9789</v>
+        <v>1.0147</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -907,10 +907,10 @@
         <v>120</v>
       </c>
       <c r="E3">
-        <v>-133</v>
+        <v>-142</v>
       </c>
       <c r="F3">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -919,7 +919,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -970,10 +970,10 @@
         <v>4.33</v>
       </c>
       <c r="AB3">
-        <v>0.8582</v>
+        <v>0.8523</v>
       </c>
       <c r="AC3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD3">
         <v>0.1858</v>
@@ -988,7 +988,7 @@
         <v>0.2188</v>
       </c>
       <c r="AH3">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI3">
         <v>0.9969</v>
@@ -997,10 +997,10 @@
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM3">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>5.5</v>
@@ -1020,10 +1020,10 @@
         <v>105</v>
       </c>
       <c r="E4">
-        <v>-119</v>
+        <v>-115</v>
       </c>
       <c r="F4">
-        <v>6.51</v>
+        <v>6.47</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1032,13 +1032,13 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>6.51</v>
+        <v>6.47</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N4">
         <v>824887</v>
@@ -1083,10 +1083,10 @@
         <v>4.29</v>
       </c>
       <c r="AB4">
-        <v>1.0937</v>
+        <v>1.0861</v>
       </c>
       <c r="AC4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD4">
         <v>0.2368</v>
@@ -1101,7 +1101,7 @@
         <v>0.2176</v>
       </c>
       <c r="AH4">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI4">
         <v>1.0158</v>
@@ -1110,10 +1110,10 @@
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1133,10 +1133,10 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>-113</v>
+        <v>-123</v>
       </c>
       <c r="F5">
-        <v>5.26</v>
+        <v>5.23</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1145,13 +1145,13 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>5.26</v>
+        <v>5.23</v>
       </c>
       <c r="L5" t="s">
         <v>46</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5">
         <v>824887</v>
@@ -1196,10 +1196,10 @@
         <v>4.18</v>
       </c>
       <c r="AB5">
-        <v>1.1497</v>
+        <v>1.1417</v>
       </c>
       <c r="AC5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD5">
         <v>0.249</v>
@@ -1214,7 +1214,7 @@
         <v>0.2248</v>
       </c>
       <c r="AH5">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI5">
         <v>0.9914</v>
@@ -1223,10 +1223,10 @@
         <v>1</v>
       </c>
       <c r="AK5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>5.5</v>
@@ -1249,7 +1249,7 @@
         <v>-134</v>
       </c>
       <c r="F6">
-        <v>5.3</v>
+        <v>5.26</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1258,13 +1258,13 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>5.26</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N6">
         <v>823675</v>
@@ -1309,10 +1309,10 @@
         <v>4.2</v>
       </c>
       <c r="AB6">
-        <v>1.1299</v>
+        <v>1.1221</v>
       </c>
       <c r="AC6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD6">
         <v>0.2447</v>
@@ -1327,7 +1327,7 @@
         <v>0.2379</v>
       </c>
       <c r="AH6">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI6">
         <v>1.0071</v>
@@ -1336,10 +1336,10 @@
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM6">
         <v>0</v>
@@ -1350,19 +1350,19 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>4.5</v>
       </c>
       <c r="D7">
-        <v>-136</v>
+        <v>-138</v>
       </c>
       <c r="E7">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F7">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1371,13 +1371,13 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N7">
         <v>823675</v>
@@ -1422,10 +1422,10 @@
         <v>4.18</v>
       </c>
       <c r="AB7">
-        <v>0.8601</v>
+        <v>0.8541</v>
       </c>
       <c r="AC7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD7">
         <v>0.1862</v>
@@ -1440,7 +1440,7 @@
         <v>0.2209</v>
       </c>
       <c r="AH7">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI7">
         <v>0.8897</v>
@@ -1449,10 +1449,10 @@
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM7">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>-135</v>
       </c>
       <c r="F8">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1484,7 +1484,7 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="L8" t="s">
         <v>46</v>
@@ -1535,10 +1535,10 @@
         <v>4.52</v>
       </c>
       <c r="AB8">
-        <v>0.955</v>
+        <v>0.9484</v>
       </c>
       <c r="AC8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD8">
         <v>0.2068</v>
@@ -1553,7 +1553,7 @@
         <v>0.212</v>
       </c>
       <c r="AH8">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI8">
         <v>0.9551</v>
@@ -1562,10 +1562,10 @@
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM8">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>-135</v>
       </c>
       <c r="F9">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1597,7 +1597,7 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="L9" t="s">
         <v>46</v>
@@ -1648,10 +1648,10 @@
         <v>4.22</v>
       </c>
       <c r="AB9">
-        <v>0.8494</v>
+        <v>0.8435</v>
       </c>
       <c r="AC9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD9">
         <v>0.1839</v>
@@ -1666,7 +1666,7 @@
         <v>0.2262</v>
       </c>
       <c r="AH9">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI9">
         <v>0.9677</v>
@@ -1675,10 +1675,10 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -1695,13 +1695,13 @@
         <v>6.5</v>
       </c>
       <c r="D10">
-        <v>-132</v>
+        <v>-128</v>
       </c>
       <c r="E10">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F10">
-        <v>7.39</v>
+        <v>7.34</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1710,7 +1710,7 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>7.39</v>
+        <v>7.34</v>
       </c>
       <c r="L10" t="s">
         <v>65</v>
@@ -1761,10 +1761,10 @@
         <v>4.11</v>
       </c>
       <c r="AB10">
-        <v>1.0432</v>
+        <v>1.036</v>
       </c>
       <c r="AC10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD10">
         <v>0.2259</v>
@@ -1779,7 +1779,7 @@
         <v>0.2496</v>
       </c>
       <c r="AH10">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI10">
         <v>1.0227</v>
@@ -1788,10 +1788,10 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -1808,13 +1808,13 @@
         <v>6.5</v>
       </c>
       <c r="D11">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E11">
         <v>-115</v>
       </c>
       <c r="F11">
-        <v>7.63</v>
+        <v>7.58</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1823,7 +1823,7 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>7.63</v>
+        <v>7.58</v>
       </c>
       <c r="L11" t="s">
         <v>65</v>
@@ -1874,10 +1874,10 @@
         <v>4.25</v>
       </c>
       <c r="AB11">
-        <v>1.2614</v>
+        <v>1.2527</v>
       </c>
       <c r="AC11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD11">
         <v>0.2731</v>
@@ -1892,7 +1892,7 @@
         <v>0.2606</v>
       </c>
       <c r="AH11">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI11">
         <v>1.0392</v>
@@ -1901,10 +1901,10 @@
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>-134</v>
       </c>
       <c r="F12">
-        <v>5.37</v>
+        <v>5.33</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1936,7 +1936,7 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>5.37</v>
+        <v>5.33</v>
       </c>
       <c r="L12" t="s">
         <v>46</v>
@@ -1987,10 +1987,10 @@
         <v>4.06</v>
       </c>
       <c r="AB12">
-        <v>1.0432</v>
+        <v>1.036</v>
       </c>
       <c r="AC12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD12">
         <v>0.2259</v>
@@ -2005,7 +2005,7 @@
         <v>0.2169</v>
       </c>
       <c r="AH12">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI12">
         <v>1.002</v>
@@ -2014,10 +2014,10 @@
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>116</v>
       </c>
       <c r="F13">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2049,7 +2049,7 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="L13" t="s">
         <v>46</v>
@@ -2100,10 +2100,10 @@
         <v>4.08</v>
       </c>
       <c r="AB13">
-        <v>0.853</v>
+        <v>0.8471</v>
       </c>
       <c r="AC13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD13">
         <v>0.1847</v>
@@ -2118,7 +2118,7 @@
         <v>0.2012</v>
       </c>
       <c r="AH13">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI13">
         <v>0.9161</v>
@@ -2127,10 +2127,10 @@
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>112</v>
       </c>
       <c r="F14">
-        <v>6.41</v>
+        <v>6.37</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2162,10 +2162,10 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>6.41</v>
+        <v>6.37</v>
       </c>
       <c r="L14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M14" t="s">
         <v>72</v>
@@ -2213,10 +2213,10 @@
         <v>4.53</v>
       </c>
       <c r="AB14">
-        <v>1.2324</v>
+        <v>1.2239</v>
       </c>
       <c r="AC14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD14">
         <v>0.2669</v>
@@ -2231,7 +2231,7 @@
         <v>0.218</v>
       </c>
       <c r="AH14">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI14">
         <v>1.029</v>
@@ -2240,10 +2240,10 @@
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>-130</v>
       </c>
       <c r="F15">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2275,7 +2275,7 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
@@ -2326,10 +2326,10 @@
         <v>4.6</v>
       </c>
       <c r="AB15">
-        <v>0.8354</v>
+        <v>0.8297</v>
       </c>
       <c r="AC15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD15">
         <v>0.1809</v>
@@ -2344,7 +2344,7 @@
         <v>0.1829</v>
       </c>
       <c r="AH15">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI15">
         <v>0.8918</v>
@@ -2353,10 +2353,10 @@
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         <v>102</v>
       </c>
       <c r="E16">
-        <v>-115</v>
+        <v>-114</v>
       </c>
       <c r="F16">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2388,7 +2388,7 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
@@ -2439,10 +2439,10 @@
         <v>3.84</v>
       </c>
       <c r="AB16">
-        <v>0.7138</v>
+        <v>0.7089</v>
       </c>
       <c r="AC16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD16">
         <v>0.1546</v>
@@ -2457,7 +2457,7 @@
         <v>0.2194</v>
       </c>
       <c r="AH16">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI16">
         <v>0.9922</v>
@@ -2466,10 +2466,10 @@
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM16">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>117</v>
       </c>
       <c r="F17">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2501,7 +2501,7 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
@@ -2552,10 +2552,10 @@
         <v>4.03</v>
       </c>
       <c r="AB17">
-        <v>1.0731</v>
+        <v>1.0657</v>
       </c>
       <c r="AC17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD17">
         <v>0.2324</v>
@@ -2570,7 +2570,7 @@
         <v>0.2137</v>
       </c>
       <c r="AH17">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI17">
         <v>0.9959</v>
@@ -2579,10 +2579,10 @@
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2599,13 +2599,10 @@
         <v>3.5</v>
       </c>
       <c r="D18">
-        <v>-130</v>
+        <v>-154</v>
       </c>
       <c r="E18">
-        <v>112</v>
-      </c>
-      <c r="F18">
-        <v>3.23</v>
+        <v>135</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2613,92 +2610,32 @@
       <c r="J18" t="s">
         <v>45</v>
       </c>
-      <c r="K18">
-        <v>3.23</v>
-      </c>
       <c r="L18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M18" t="s">
         <v>79</v>
       </c>
-      <c r="N18">
-        <v>823189</v>
+      <c r="N18" t="s">
+        <v>45</v>
       </c>
       <c r="O18" t="s">
-        <v>48</v>
-      </c>
-      <c r="P18">
-        <v>5</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S18">
         <v>6</v>
       </c>
-      <c r="T18">
-        <v>0.1884</v>
-      </c>
-      <c r="U18">
-        <v>0.1832</v>
-      </c>
-      <c r="V18">
-        <v>1</v>
-      </c>
-      <c r="W18">
-        <v>22</v>
-      </c>
-      <c r="X18">
-        <v>0.1364</v>
-      </c>
-      <c r="Y18">
-        <v>0.099</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>4.06</v>
-      </c>
-      <c r="AB18">
-        <v>0.842</v>
-      </c>
       <c r="AC18" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD18">
-        <v>0.1823</v>
-      </c>
-      <c r="AE18">
-        <v>0.1944</v>
-      </c>
-      <c r="AF18">
-        <v>9</v>
-      </c>
-      <c r="AG18">
-        <v>0.2171</v>
-      </c>
-      <c r="AH18">
-        <v>0.2166</v>
-      </c>
-      <c r="AI18">
-        <v>1.0304</v>
-      </c>
-      <c r="AJ18" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>45</v>
       </c>
       <c r="AK18" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AL18" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
@@ -2712,10 +2649,13 @@
         <v>3.5</v>
       </c>
       <c r="D19">
-        <v>-154</v>
+        <v>-130</v>
       </c>
       <c r="E19">
-        <v>135</v>
+        <v>112</v>
+      </c>
+      <c r="F19">
+        <v>3.2</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2723,32 +2663,92 @@
       <c r="J19" t="s">
         <v>45</v>
       </c>
+      <c r="K19">
+        <v>3.2</v>
+      </c>
       <c r="L19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M19" t="s">
         <v>79</v>
       </c>
-      <c r="N19" t="s">
-        <v>45</v>
+      <c r="N19">
+        <v>823189</v>
       </c>
       <c r="O19" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P19">
+        <v>5</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
       </c>
       <c r="S19">
         <v>6</v>
       </c>
+      <c r="T19">
+        <v>0.1884</v>
+      </c>
+      <c r="U19">
+        <v>0.1832</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>22</v>
+      </c>
+      <c r="X19">
+        <v>0.1364</v>
+      </c>
+      <c r="Y19">
+        <v>0.099</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>4.06</v>
+      </c>
+      <c r="AB19">
+        <v>0.8362</v>
+      </c>
       <c r="AC19" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>45</v>
+        <v>52</v>
+      </c>
+      <c r="AD19">
+        <v>0.1823</v>
+      </c>
+      <c r="AE19">
+        <v>0.1944</v>
+      </c>
+      <c r="AF19">
+        <v>9</v>
+      </c>
+      <c r="AG19">
+        <v>0.2171</v>
+      </c>
+      <c r="AH19">
+        <v>0.2181</v>
+      </c>
+      <c r="AI19">
+        <v>1.0304</v>
+      </c>
+      <c r="AJ19" t="b">
+        <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AL19" t="s">
-        <v>45</v>
+        <v>53</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
@@ -2765,10 +2765,10 @@
         <v>-118</v>
       </c>
       <c r="E20">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F20">
-        <v>6.34</v>
+        <v>6.3</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2777,10 +2777,10 @@
         <v>45</v>
       </c>
       <c r="K20">
-        <v>6.34</v>
+        <v>6.3</v>
       </c>
       <c r="L20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M20" t="s">
         <v>82</v>
@@ -2828,10 +2828,10 @@
         <v>3.88</v>
       </c>
       <c r="AB20">
-        <v>0.9337</v>
+        <v>0.9273</v>
       </c>
       <c r="AC20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD20">
         <v>0.2022</v>
@@ -2846,7 +2846,7 @@
         <v>0.2091</v>
       </c>
       <c r="AH20">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI20">
         <v>0.941</v>
@@ -2855,10 +2855,10 @@
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM20">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>120</v>
       </c>
       <c r="F21">
-        <v>7.45</v>
+        <v>7.39</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2890,7 +2890,7 @@
         <v>45</v>
       </c>
       <c r="K21">
-        <v>7.45</v>
+        <v>7.39</v>
       </c>
       <c r="L21" t="s">
         <v>65</v>
@@ -2941,10 +2941,10 @@
         <v>4.26</v>
       </c>
       <c r="AB21">
-        <v>1.3715</v>
+        <v>1.3621</v>
       </c>
       <c r="AC21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AD21">
         <v>0.297</v>
@@ -2959,7 +2959,7 @@
         <v>0.2004</v>
       </c>
       <c r="AH21">
-        <v>0.2166</v>
+        <v>0.2181</v>
       </c>
       <c r="AI21">
         <v>0.9913</v>
@@ -2968,10 +2968,10 @@
         <v>1</v>
       </c>
       <c r="AK21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AL21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AM21">
         <v>0</v>

--- a/data/k-props/2026-08-10.xlsx
+++ b/data/k-props/2026-08-10.xlsx
@@ -169,63 +169,63 @@
     <t>Jameson Taillon</t>
   </si>
   <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>New York Mets @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Bryce Elder</t>
+  </si>
+  <si>
+    <t>Trevor Rogers</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ St. Louis Cardinals</t>
+  </si>
+  <si>
+    <t>Hunter Dobbins</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Los Angeles Angels</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
   </si>
   <si>
-    <t>Christian Scott</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>New York Mets @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Bryce Elder</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Trevor Rogers</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ St. Louis Cardinals</t>
-  </si>
-  <si>
-    <t>Hunter Dobbins</t>
-  </si>
-  <si>
     <t>Reid Detmers</t>
   </si>
   <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
+    <t>Gabriel Hughes</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Arizona Diamondbacks</t>
   </si>
   <si>
     <t>Michael Soroka</t>
   </si>
   <si>
-    <t>Colorado Rockies @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Gabriel Hughes</t>
-  </si>
-  <si>
     <t>Freddy Peralta</t>
   </si>
   <si>
@@ -247,22 +247,22 @@
     <t>Casey Mize</t>
   </si>
   <si>
+    <t>Blade Tidwell</t>
+  </si>
+  <si>
+    <t>Houston Astros @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
     <t>Hayden Wesneski</t>
-  </si>
-  <si>
-    <t>Houston Astros @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Blade Tidwell</t>
-  </si>
-  <si>
-    <t>Tarik Skubal</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Noah Cameron</t>
   </si>
 </sst>
 </file>
@@ -791,13 +791,13 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-119</v>
+        <v>-132</v>
       </c>
       <c r="E2">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F2">
-        <v>5.17</v>
+        <v>4.53</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -806,7 +806,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>5.17</v>
+        <v>4.53</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2">
         <v>0.219</v>
@@ -857,28 +857,28 @@
         <v>4.04</v>
       </c>
       <c r="AB2">
-        <v>1.0606</v>
+        <v>0.9971</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
       </c>
       <c r="AD2">
-        <v>0.2313</v>
+        <v>0.2201</v>
       </c>
       <c r="AE2">
-        <v>0.2159</v>
+        <v>0.1917</v>
       </c>
       <c r="AF2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG2">
         <v>0.1891</v>
       </c>
       <c r="AH2">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI2">
-        <v>1.0147</v>
+        <v>0.9458</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -904,13 +904,13 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E3">
-        <v>-142</v>
+        <v>-138</v>
       </c>
       <c r="F3">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -919,7 +919,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -970,37 +970,37 @@
         <v>4.33</v>
       </c>
       <c r="AB3">
-        <v>0.8523</v>
+        <v>0.8918</v>
       </c>
       <c r="AC3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD3">
-        <v>0.1858</v>
+        <v>0.1968</v>
       </c>
       <c r="AE3">
-        <v>0.1843</v>
+        <v>0.1918</v>
       </c>
       <c r="AF3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG3">
         <v>0.2188</v>
       </c>
       <c r="AH3">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI3">
-        <v>0.9969</v>
+        <v>1.0162</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM3">
         <v>0</v>
@@ -1011,19 +1011,19 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4">
         <v>5.5</v>
       </c>
       <c r="D4">
-        <v>105</v>
+        <v>-112</v>
       </c>
       <c r="E4">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F4">
-        <v>6.47</v>
+        <v>6.66</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1032,13 +1032,13 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>6.47</v>
+        <v>6.66</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N4">
         <v>824887</v>
@@ -1083,16 +1083,16 @@
         <v>4.29</v>
       </c>
       <c r="AB4">
-        <v>1.0861</v>
+        <v>1.0937</v>
       </c>
       <c r="AC4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD4">
-        <v>0.2368</v>
+        <v>0.2414</v>
       </c>
       <c r="AE4">
-        <v>0.228</v>
+        <v>0.2117</v>
       </c>
       <c r="AF4">
         <v>9</v>
@@ -1101,19 +1101,19 @@
         <v>0.2176</v>
       </c>
       <c r="AH4">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI4">
-        <v>1.0158</v>
+        <v>1.0388</v>
       </c>
       <c r="AJ4" t="b">
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>4.5</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E5">
-        <v>-123</v>
+        <v>-120</v>
       </c>
       <c r="F5">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1145,13 +1145,13 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="L5" t="s">
         <v>46</v>
       </c>
       <c r="M5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N5">
         <v>824887</v>
@@ -1196,37 +1196,37 @@
         <v>4.18</v>
       </c>
       <c r="AB5">
-        <v>1.1417</v>
+        <v>1.1691</v>
       </c>
       <c r="AC5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD5">
-        <v>0.249</v>
+        <v>0.258</v>
       </c>
       <c r="AE5">
-        <v>0.2485</v>
+        <v>0.2517</v>
       </c>
       <c r="AF5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG5">
         <v>0.2248</v>
       </c>
       <c r="AH5">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI5">
-        <v>0.9914</v>
+        <v>0.9771</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
       </c>
       <c r="AK5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -1237,19 +1237,19 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D6">
-        <v>116</v>
+        <v>-130</v>
       </c>
       <c r="E6">
-        <v>-134</v>
+        <v>105</v>
       </c>
       <c r="F6">
-        <v>5.26</v>
+        <v>3.91</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1258,13 +1258,13 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>5.26</v>
+        <v>3.91</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N6">
         <v>823675</v>
@@ -1273,7 +1273,7 @@
         <v>48</v>
       </c>
       <c r="P6">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1285,61 +1285,61 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>0.2326</v>
+        <v>0.2025</v>
       </c>
       <c r="U6">
-        <v>0.2167</v>
+        <v>0.2261</v>
       </c>
       <c r="V6">
         <v>5</v>
       </c>
       <c r="W6">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="X6">
-        <v>0.1869</v>
+        <v>0.264</v>
       </c>
       <c r="Y6">
-        <v>0.349</v>
+        <v>0.385</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="AB6">
-        <v>1.1221</v>
+        <v>0.8438</v>
       </c>
       <c r="AC6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD6">
-        <v>0.2447</v>
+        <v>0.1862</v>
       </c>
       <c r="AE6">
-        <v>0.2682</v>
+        <v>0.1904</v>
       </c>
       <c r="AF6">
         <v>9</v>
       </c>
       <c r="AG6">
-        <v>0.2379</v>
+        <v>0.2209</v>
       </c>
       <c r="AH6">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI6">
-        <v>1.0071</v>
+        <v>0.8897</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM6">
         <v>0</v>
@@ -1350,19 +1350,19 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D7">
-        <v>-138</v>
+        <v>117</v>
       </c>
       <c r="E7">
-        <v>116</v>
+        <v>-143</v>
       </c>
       <c r="F7">
-        <v>3.96</v>
+        <v>6.34</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1371,13 +1371,13 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>3.96</v>
+        <v>6.34</v>
       </c>
       <c r="L7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N7">
         <v>823675</v>
@@ -1386,7 +1386,7 @@
         <v>48</v>
       </c>
       <c r="P7">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1398,52 +1398,52 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>0.2025</v>
+        <v>0.2326</v>
       </c>
       <c r="U7">
-        <v>0.2261</v>
+        <v>0.2167</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="X7">
-        <v>0.264</v>
+        <v>0.1869</v>
       </c>
       <c r="Y7">
-        <v>0.385</v>
+        <v>0.349</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="AB7">
-        <v>0.8541</v>
+        <v>1.2986</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
       </c>
       <c r="AD7">
-        <v>0.1862</v>
+        <v>0.2866</v>
       </c>
       <c r="AE7">
-        <v>0.1904</v>
+        <v>0.2763</v>
       </c>
       <c r="AF7">
         <v>9</v>
       </c>
       <c r="AG7">
-        <v>0.2209</v>
+        <v>0.2379</v>
       </c>
       <c r="AH7">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI7">
-        <v>0.8897</v>
+        <v>1.0489</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
@@ -1463,7 +1463,7 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1472,10 +1472,10 @@
         <v>110</v>
       </c>
       <c r="E8">
-        <v>-135</v>
+        <v>-125</v>
       </c>
       <c r="F8">
-        <v>3.66</v>
+        <v>3.43</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1484,13 +1484,13 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>3.66</v>
+        <v>3.43</v>
       </c>
       <c r="L8" t="s">
         <v>46</v>
       </c>
       <c r="M8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N8">
         <v>823018</v>
@@ -1535,37 +1535,37 @@
         <v>4.52</v>
       </c>
       <c r="AB8">
-        <v>0.9484</v>
+        <v>0.945</v>
       </c>
       <c r="AC8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD8">
-        <v>0.2068</v>
+        <v>0.2086</v>
       </c>
       <c r="AE8">
-        <v>0.1839</v>
+        <v>0.1893</v>
       </c>
       <c r="AF8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8">
         <v>0.212</v>
       </c>
       <c r="AH8">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI8">
-        <v>0.9551</v>
+        <v>0.8995</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM8">
         <v>0</v>
@@ -1576,19 +1576,19 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>3.5</v>
       </c>
       <c r="D9">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E9">
-        <v>-135</v>
+        <v>-118</v>
       </c>
       <c r="F9">
-        <v>3.73</v>
+        <v>4.39</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1597,13 +1597,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>3.73</v>
+        <v>4.39</v>
       </c>
       <c r="L9" t="s">
         <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N9">
         <v>823018</v>
@@ -1648,16 +1648,16 @@
         <v>4.22</v>
       </c>
       <c r="AB9">
-        <v>0.8435</v>
+        <v>1.0057</v>
       </c>
       <c r="AC9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD9">
-        <v>0.1839</v>
+        <v>0.222</v>
       </c>
       <c r="AE9">
-        <v>0.1876</v>
+        <v>0.2061</v>
       </c>
       <c r="AF9">
         <v>9</v>
@@ -1666,19 +1666,19 @@
         <v>0.2262</v>
       </c>
       <c r="AH9">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI9">
-        <v>0.9677</v>
+        <v>0.957</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -1689,19 +1689,19 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>6.5</v>
       </c>
       <c r="D10">
-        <v>-128</v>
+        <v>104</v>
       </c>
       <c r="E10">
-        <v>110</v>
+        <v>-115</v>
       </c>
       <c r="F10">
-        <v>7.34</v>
+        <v>7.49</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1710,13 +1710,13 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>7.34</v>
+        <v>7.49</v>
       </c>
       <c r="L10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N10">
         <v>823998</v>
@@ -1725,7 +1725,7 @@
         <v>48</v>
       </c>
       <c r="P10">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1737,61 +1737,61 @@
         <v>6</v>
       </c>
       <c r="T10">
-        <v>0.283</v>
+        <v>0.2559</v>
       </c>
       <c r="U10">
-        <v>0.3007</v>
+        <v>0.2554</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="X10">
-        <v>0.3367</v>
+        <v>0.2544</v>
       </c>
       <c r="Y10">
-        <v>0.329</v>
+        <v>0.363</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>4.11</v>
+        <v>4.25</v>
       </c>
       <c r="AB10">
-        <v>1.036</v>
+        <v>1.2376</v>
       </c>
       <c r="AC10" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="AD10">
-        <v>0.2259</v>
+        <v>0.2731</v>
       </c>
       <c r="AE10">
-        <v>0.2363</v>
+        <v>0.2647</v>
       </c>
       <c r="AF10">
         <v>9</v>
       </c>
       <c r="AG10">
-        <v>0.2496</v>
+        <v>0.2606</v>
       </c>
       <c r="AH10">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI10">
-        <v>1.0227</v>
+        <v>1.0392</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AL10" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -1808,13 +1808,13 @@
         <v>6.5</v>
       </c>
       <c r="D11">
-        <v>104</v>
+        <v>-128</v>
       </c>
       <c r="E11">
-        <v>-115</v>
+        <v>110</v>
       </c>
       <c r="F11">
-        <v>7.58</v>
+        <v>7.25</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1823,13 +1823,13 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>7.58</v>
+        <v>7.25</v>
       </c>
       <c r="L11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N11">
         <v>823998</v>
@@ -1838,7 +1838,7 @@
         <v>48</v>
       </c>
       <c r="P11">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
@@ -1850,61 +1850,61 @@
         <v>6</v>
       </c>
       <c r="T11">
-        <v>0.2559</v>
+        <v>0.283</v>
       </c>
       <c r="U11">
-        <v>0.2554</v>
+        <v>0.3007</v>
       </c>
       <c r="V11">
         <v>5</v>
       </c>
       <c r="W11">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="X11">
-        <v>0.2544</v>
+        <v>0.3367</v>
       </c>
       <c r="Y11">
-        <v>0.363</v>
+        <v>0.329</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="AB11">
-        <v>1.2527</v>
+        <v>1.0236</v>
       </c>
       <c r="AC11" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="AD11">
-        <v>0.2731</v>
+        <v>0.2259</v>
       </c>
       <c r="AE11">
-        <v>0.2647</v>
+        <v>0.2363</v>
       </c>
       <c r="AF11">
         <v>9</v>
       </c>
       <c r="AG11">
-        <v>0.2606</v>
+        <v>0.2496</v>
       </c>
       <c r="AH11">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI11">
-        <v>1.0392</v>
+        <v>1.0227</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AL11" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -1918,16 +1918,16 @@
         <v>68</v>
       </c>
       <c r="C12">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D12">
+        <v>-125</v>
+      </c>
+      <c r="E12">
         <v>116</v>
       </c>
-      <c r="E12">
-        <v>-134</v>
-      </c>
       <c r="F12">
-        <v>5.33</v>
+        <v>4.02</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1936,7 +1936,7 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>5.33</v>
+        <v>4.02</v>
       </c>
       <c r="L12" t="s">
         <v>46</v>
@@ -1951,7 +1951,7 @@
         <v>48</v>
       </c>
       <c r="P12">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1963,61 +1963,61 @@
         <v>6</v>
       </c>
       <c r="T12">
-        <v>0.2372</v>
+        <v>0.2314</v>
       </c>
       <c r="U12">
-        <v>0.2315</v>
+        <v>0.2364</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="X12">
-        <v>0.22</v>
+        <v>0.2455</v>
       </c>
       <c r="Y12">
-        <v>0.333</v>
+        <v>0.355</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="AB12">
-        <v>1.036</v>
+        <v>0.8874</v>
       </c>
       <c r="AC12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD12">
-        <v>0.2259</v>
+        <v>0.1959</v>
       </c>
       <c r="AE12">
-        <v>0.2243</v>
+        <v>0.1921</v>
       </c>
       <c r="AF12">
         <v>9</v>
       </c>
       <c r="AG12">
-        <v>0.2169</v>
+        <v>0.2012</v>
       </c>
       <c r="AH12">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI12">
-        <v>1.002</v>
+        <v>0.88</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -2031,16 +2031,16 @@
         <v>70</v>
       </c>
       <c r="C13">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D13">
-        <v>-126</v>
+        <v>114</v>
       </c>
       <c r="E13">
-        <v>116</v>
+        <v>-138</v>
       </c>
       <c r="F13">
-        <v>3.99</v>
+        <v>5.42</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2049,7 +2049,7 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>3.99</v>
+        <v>5.42</v>
       </c>
       <c r="L13" t="s">
         <v>46</v>
@@ -2064,7 +2064,7 @@
         <v>48</v>
       </c>
       <c r="P13">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -2076,61 +2076,61 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>0.2314</v>
+        <v>0.2372</v>
       </c>
       <c r="U13">
-        <v>0.2364</v>
+        <v>0.2315</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="X13">
-        <v>0.2455</v>
+        <v>0.22</v>
       </c>
       <c r="Y13">
-        <v>0.355</v>
+        <v>0.333</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="AB13">
-        <v>0.8471</v>
+        <v>1.0474</v>
       </c>
       <c r="AC13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD13">
-        <v>0.1847</v>
+        <v>0.2312</v>
       </c>
       <c r="AE13">
-        <v>0.183</v>
+        <v>0.2224</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
       <c r="AG13">
-        <v>0.2012</v>
+        <v>0.2169</v>
       </c>
       <c r="AH13">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI13">
-        <v>0.9161</v>
+        <v>1.006</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2147,13 +2147,13 @@
         <v>4.5</v>
       </c>
       <c r="D14">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="E14">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F14">
-        <v>6.37</v>
+        <v>4.66</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2162,10 +2162,10 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>6.37</v>
+        <v>4.66</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="M14" t="s">
         <v>72</v>
@@ -2213,37 +2213,37 @@
         <v>4.53</v>
       </c>
       <c r="AB14">
-        <v>1.2239</v>
+        <v>0.9345</v>
       </c>
       <c r="AC14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD14">
-        <v>0.2669</v>
+        <v>0.2063</v>
       </c>
       <c r="AE14">
-        <v>0.2349</v>
+        <v>0.2082</v>
       </c>
       <c r="AF14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG14">
         <v>0.218</v>
       </c>
       <c r="AH14">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI14">
-        <v>1.029</v>
+        <v>0.9863</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2260,13 +2260,13 @@
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E15">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="F15">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2275,7 +2275,7 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
@@ -2326,10 +2326,10 @@
         <v>4.6</v>
       </c>
       <c r="AB15">
-        <v>0.8297</v>
+        <v>0.8197</v>
       </c>
       <c r="AC15" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="AD15">
         <v>0.1809</v>
@@ -2344,7 +2344,7 @@
         <v>0.1829</v>
       </c>
       <c r="AH15">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI15">
         <v>0.8918</v>
@@ -2353,10 +2353,10 @@
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AL15" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2373,13 +2373,13 @@
         <v>5.5</v>
       </c>
       <c r="D16">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E16">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="F16">
-        <v>4.32</v>
+        <v>4.87</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2388,7 +2388,7 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.32</v>
+        <v>4.87</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
@@ -2439,16 +2439,16 @@
         <v>3.84</v>
       </c>
       <c r="AB16">
-        <v>0.7089</v>
+        <v>0.7959</v>
       </c>
       <c r="AC16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD16">
-        <v>0.1546</v>
+        <v>0.1757</v>
       </c>
       <c r="AE16">
-        <v>0.1723</v>
+        <v>0.178</v>
       </c>
       <c r="AF16">
         <v>9</v>
@@ -2457,19 +2457,19 @@
         <v>0.2194</v>
       </c>
       <c r="AH16">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI16">
-        <v>0.9922</v>
+        <v>0.9963</v>
       </c>
       <c r="AJ16" t="b">
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM16">
         <v>0</v>
@@ -2486,13 +2486,13 @@
         <v>4.5</v>
       </c>
       <c r="D17">
-        <v>-137</v>
+        <v>-136</v>
       </c>
       <c r="E17">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F17">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2501,7 +2501,7 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
@@ -2552,10 +2552,10 @@
         <v>4.03</v>
       </c>
       <c r="AB17">
-        <v>1.0657</v>
+        <v>1.0528</v>
       </c>
       <c r="AC17" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="AD17">
         <v>0.2324</v>
@@ -2570,7 +2570,7 @@
         <v>0.2137</v>
       </c>
       <c r="AH17">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI17">
         <v>0.9959</v>
@@ -2579,10 +2579,10 @@
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AL17" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2599,10 +2599,13 @@
         <v>3.5</v>
       </c>
       <c r="D18">
-        <v>-154</v>
+        <v>-134</v>
       </c>
       <c r="E18">
-        <v>135</v>
+        <v>110</v>
+      </c>
+      <c r="F18">
+        <v>3.17</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2610,32 +2613,92 @@
       <c r="J18" t="s">
         <v>45</v>
       </c>
+      <c r="K18">
+        <v>3.17</v>
+      </c>
       <c r="L18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M18" t="s">
         <v>79</v>
       </c>
-      <c r="N18" t="s">
-        <v>45</v>
+      <c r="N18">
+        <v>823189</v>
       </c>
       <c r="O18" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P18">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
       </c>
       <c r="S18">
         <v>6</v>
       </c>
+      <c r="T18">
+        <v>0.1884</v>
+      </c>
+      <c r="U18">
+        <v>0.1832</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>22</v>
+      </c>
+      <c r="X18">
+        <v>0.1364</v>
+      </c>
+      <c r="Y18">
+        <v>0.099</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>4.06</v>
+      </c>
+      <c r="AB18">
+        <v>0.8261</v>
+      </c>
       <c r="AC18" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>45</v>
+        <v>65</v>
+      </c>
+      <c r="AD18">
+        <v>0.1823</v>
+      </c>
+      <c r="AE18">
+        <v>0.1944</v>
+      </c>
+      <c r="AF18">
+        <v>9</v>
+      </c>
+      <c r="AG18">
+        <v>0.2171</v>
+      </c>
+      <c r="AH18">
+        <v>0.2207</v>
+      </c>
+      <c r="AI18">
+        <v>1.0304</v>
+      </c>
+      <c r="AJ18" t="b">
+        <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="AL18" t="s">
-        <v>45</v>
+        <v>66</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
@@ -2646,16 +2709,16 @@
         <v>80</v>
       </c>
       <c r="C19">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>-130</v>
+        <v>-146</v>
       </c>
       <c r="E19">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F19">
-        <v>3.2</v>
+        <v>7.3</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2664,22 +2727,22 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>3.2</v>
+        <v>7.3</v>
       </c>
       <c r="L19" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="M19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N19">
-        <v>823189</v>
+        <v>823918</v>
       </c>
       <c r="O19" t="s">
         <v>48</v>
       </c>
       <c r="P19">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -2691,61 +2754,61 @@
         <v>6</v>
       </c>
       <c r="T19">
-        <v>0.1884</v>
+        <v>0.2201</v>
       </c>
       <c r="U19">
-        <v>0.1832</v>
+        <v>0.2313</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="X19">
-        <v>0.1364</v>
+        <v>0.2481</v>
       </c>
       <c r="Y19">
-        <v>0.099</v>
+        <v>0.399</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>4.06</v>
+        <v>4.26</v>
       </c>
       <c r="AB19">
-        <v>0.8362</v>
+        <v>1.3457</v>
       </c>
       <c r="AC19" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="AD19">
-        <v>0.1823</v>
+        <v>0.297</v>
       </c>
       <c r="AE19">
-        <v>0.1944</v>
+        <v>0.2256</v>
       </c>
       <c r="AF19">
         <v>9</v>
       </c>
       <c r="AG19">
-        <v>0.2171</v>
+        <v>0.2004</v>
       </c>
       <c r="AH19">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI19">
-        <v>1.0304</v>
+        <v>0.9913</v>
       </c>
       <c r="AJ19" t="b">
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AL19" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AM19">
         <v>0</v>
@@ -2756,19 +2819,19 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C20">
         <v>7.5</v>
       </c>
       <c r="D20">
-        <v>-118</v>
+        <v>-113</v>
       </c>
       <c r="E20">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F20">
-        <v>6.3</v>
+        <v>5.55</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2777,13 +2840,13 @@
         <v>45</v>
       </c>
       <c r="K20">
-        <v>6.3</v>
+        <v>5.55</v>
       </c>
       <c r="L20" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N20">
         <v>823918</v>
@@ -2828,37 +2891,37 @@
         <v>3.88</v>
       </c>
       <c r="AB20">
-        <v>0.9273</v>
+        <v>0.8306</v>
       </c>
       <c r="AC20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD20">
-        <v>0.2022</v>
+        <v>0.1833</v>
       </c>
       <c r="AE20">
-        <v>0.2056</v>
+        <v>0.1991</v>
       </c>
       <c r="AF20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG20">
         <v>0.2091</v>
       </c>
       <c r="AH20">
-        <v>0.2181</v>
+        <v>0.2207</v>
       </c>
       <c r="AI20">
-        <v>0.941</v>
+        <v>0.9259</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AM20">
         <v>0</v>
@@ -2872,16 +2935,13 @@
         <v>83</v>
       </c>
       <c r="C21">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D21">
-        <v>-141</v>
+        <v>-162</v>
       </c>
       <c r="E21">
-        <v>120</v>
-      </c>
-      <c r="F21">
-        <v>7.39</v>
+        <v>134</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2889,92 +2949,32 @@
       <c r="J21" t="s">
         <v>45</v>
       </c>
-      <c r="K21">
-        <v>7.39</v>
-      </c>
       <c r="L21" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="M21" t="s">
-        <v>82</v>
-      </c>
-      <c r="N21">
-        <v>823918</v>
+        <v>79</v>
+      </c>
+      <c r="N21" t="s">
+        <v>45</v>
       </c>
       <c r="O21" t="s">
-        <v>48</v>
-      </c>
-      <c r="P21">
-        <v>5.6</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>0</v>
-      </c>
-      <c r="R21" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S21">
         <v>6</v>
       </c>
-      <c r="T21">
-        <v>0.2201</v>
-      </c>
-      <c r="U21">
-        <v>0.2313</v>
-      </c>
-      <c r="V21">
-        <v>5</v>
-      </c>
-      <c r="W21">
-        <v>133</v>
-      </c>
-      <c r="X21">
-        <v>0.2481</v>
-      </c>
-      <c r="Y21">
-        <v>0.399</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>4.26</v>
-      </c>
-      <c r="AB21">
-        <v>1.3621</v>
-      </c>
       <c r="AC21" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD21">
-        <v>0.297</v>
-      </c>
-      <c r="AE21">
-        <v>0.2256</v>
-      </c>
-      <c r="AF21">
-        <v>9</v>
-      </c>
-      <c r="AG21">
-        <v>0.2004</v>
-      </c>
-      <c r="AH21">
-        <v>0.2181</v>
-      </c>
-      <c r="AI21">
-        <v>0.9913</v>
-      </c>
-      <c r="AJ21" t="b">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>45</v>
       </c>
       <c r="AK21" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AL21" t="s">
-        <v>53</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-10.xlsx
+++ b/data/k-props/2026-08-10.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="82">
   <si>
     <t>date</t>
   </si>
@@ -206,12 +206,6 @@
   </si>
   <si>
     <t>Texas Rangers @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>projected_regulars</t>
   </si>
   <si>
     <t>Reid Detmers</t>
@@ -797,7 +791,7 @@
         <v>120</v>
       </c>
       <c r="F2">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -806,7 +800,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -857,7 +851,7 @@
         <v>4.04</v>
       </c>
       <c r="AB2">
-        <v>0.9971</v>
+        <v>0.9895</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
@@ -875,7 +869,7 @@
         <v>0.1891</v>
       </c>
       <c r="AH2">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI2">
         <v>0.9458</v>
@@ -910,7 +904,7 @@
         <v>-138</v>
       </c>
       <c r="F3">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -919,7 +913,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -970,7 +964,7 @@
         <v>4.33</v>
       </c>
       <c r="AB3">
-        <v>0.8918</v>
+        <v>0.8849</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
@@ -988,7 +982,7 @@
         <v>0.2188</v>
       </c>
       <c r="AH3">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI3">
         <v>1.0162</v>
@@ -1023,7 +1017,7 @@
         <v>-110</v>
       </c>
       <c r="F4">
-        <v>6.66</v>
+        <v>6.61</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1032,7 +1026,7 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>6.66</v>
+        <v>6.61</v>
       </c>
       <c r="L4" t="s">
         <v>53</v>
@@ -1083,7 +1077,7 @@
         <v>4.29</v>
       </c>
       <c r="AB4">
-        <v>1.0937</v>
+        <v>1.0853</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
@@ -1101,7 +1095,7 @@
         <v>0.2176</v>
       </c>
       <c r="AH4">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI4">
         <v>1.0388</v>
@@ -1136,7 +1130,7 @@
         <v>-120</v>
       </c>
       <c r="F5">
-        <v>5.28</v>
+        <v>5.24</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1145,7 +1139,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>5.28</v>
+        <v>5.24</v>
       </c>
       <c r="L5" t="s">
         <v>46</v>
@@ -1196,7 +1190,7 @@
         <v>4.18</v>
       </c>
       <c r="AB5">
-        <v>1.1691</v>
+        <v>1.1602</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
@@ -1214,7 +1208,7 @@
         <v>0.2248</v>
       </c>
       <c r="AH5">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI5">
         <v>0.9771</v>
@@ -1249,7 +1243,7 @@
         <v>105</v>
       </c>
       <c r="F6">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1258,7 +1252,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
@@ -1309,7 +1303,7 @@
         <v>4.18</v>
       </c>
       <c r="AB6">
-        <v>0.8438</v>
+        <v>0.8374</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
@@ -1327,7 +1321,7 @@
         <v>0.2209</v>
       </c>
       <c r="AH6">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI6">
         <v>0.8897</v>
@@ -1362,7 +1356,7 @@
         <v>-143</v>
       </c>
       <c r="F7">
-        <v>6.34</v>
+        <v>6.3</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1371,7 +1365,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>6.34</v>
+        <v>6.3</v>
       </c>
       <c r="L7" t="s">
         <v>53</v>
@@ -1422,7 +1416,7 @@
         <v>4.2</v>
       </c>
       <c r="AB7">
-        <v>1.2986</v>
+        <v>1.2887</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
@@ -1440,7 +1434,7 @@
         <v>0.2379</v>
       </c>
       <c r="AH7">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI7">
         <v>1.0489</v>
@@ -1475,7 +1469,7 @@
         <v>-125</v>
       </c>
       <c r="F8">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1484,7 +1478,7 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="L8" t="s">
         <v>46</v>
@@ -1535,7 +1529,7 @@
         <v>4.52</v>
       </c>
       <c r="AB8">
-        <v>0.945</v>
+        <v>0.9378</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
@@ -1553,7 +1547,7 @@
         <v>0.212</v>
       </c>
       <c r="AH8">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI8">
         <v>0.8995</v>
@@ -1588,7 +1582,7 @@
         <v>-118</v>
       </c>
       <c r="F9">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1597,7 +1591,7 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="L9" t="s">
         <v>46</v>
@@ -1648,7 +1642,7 @@
         <v>4.22</v>
       </c>
       <c r="AB9">
-        <v>1.0057</v>
+        <v>0.998</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
@@ -1666,7 +1660,7 @@
         <v>0.2262</v>
       </c>
       <c r="AH9">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI9">
         <v>0.957</v>
@@ -1701,7 +1695,7 @@
         <v>-115</v>
       </c>
       <c r="F10">
-        <v>7.49</v>
+        <v>7.66</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1710,7 +1704,7 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>7.49</v>
+        <v>7.66</v>
       </c>
       <c r="L10" t="s">
         <v>63</v>
@@ -1761,16 +1755,16 @@
         <v>4.25</v>
       </c>
       <c r="AB10">
-        <v>1.2376</v>
+        <v>1.2845</v>
       </c>
       <c r="AC10" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AD10">
-        <v>0.2731</v>
+        <v>0.2857</v>
       </c>
       <c r="AE10">
-        <v>0.2647</v>
+        <v>0.2554</v>
       </c>
       <c r="AF10">
         <v>9</v>
@@ -1779,19 +1773,19 @@
         <v>0.2606</v>
       </c>
       <c r="AH10">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI10">
-        <v>1.0392</v>
+        <v>1.024</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -1802,7 +1796,7 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C11">
         <v>6.5</v>
@@ -1814,7 +1808,7 @@
         <v>110</v>
       </c>
       <c r="F11">
-        <v>7.25</v>
+        <v>10.01</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1823,7 +1817,7 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>7.25</v>
+        <v>10.01</v>
       </c>
       <c r="L11" t="s">
         <v>63</v>
@@ -1874,16 +1868,16 @@
         <v>4.11</v>
       </c>
       <c r="AB11">
-        <v>1.0236</v>
+        <v>1.3326</v>
       </c>
       <c r="AC11" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AD11">
-        <v>0.2259</v>
+        <v>0.2964</v>
       </c>
       <c r="AE11">
-        <v>0.2363</v>
+        <v>0.2663</v>
       </c>
       <c r="AF11">
         <v>9</v>
@@ -1892,19 +1886,19 @@
         <v>0.2496</v>
       </c>
       <c r="AH11">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI11">
-        <v>1.0227</v>
+        <v>1.084</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -1915,7 +1909,7 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>3.5</v>
@@ -1927,7 +1921,7 @@
         <v>116</v>
       </c>
       <c r="F12">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1936,13 +1930,13 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="L12" t="s">
         <v>46</v>
       </c>
       <c r="M12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N12">
         <v>825048</v>
@@ -1987,7 +1981,7 @@
         <v>4.08</v>
       </c>
       <c r="AB12">
-        <v>0.8874</v>
+        <v>0.8806</v>
       </c>
       <c r="AC12" t="s">
         <v>49</v>
@@ -2005,7 +1999,7 @@
         <v>0.2012</v>
       </c>
       <c r="AH12">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI12">
         <v>0.88</v>
@@ -2028,7 +2022,7 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -2040,7 +2034,7 @@
         <v>-138</v>
       </c>
       <c r="F13">
-        <v>5.42</v>
+        <v>5.37</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2049,13 +2043,13 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>5.42</v>
+        <v>5.37</v>
       </c>
       <c r="L13" t="s">
         <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N13">
         <v>825048</v>
@@ -2100,7 +2094,7 @@
         <v>4.06</v>
       </c>
       <c r="AB13">
-        <v>1.0474</v>
+        <v>1.0394</v>
       </c>
       <c r="AC13" t="s">
         <v>49</v>
@@ -2118,7 +2112,7 @@
         <v>0.2169</v>
       </c>
       <c r="AH13">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI13">
         <v>1.006</v>
@@ -2141,7 +2135,7 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14">
         <v>4.5</v>
@@ -2153,7 +2147,7 @@
         <v>116</v>
       </c>
       <c r="F14">
-        <v>4.66</v>
+        <v>4.63</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2162,13 +2156,13 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.66</v>
+        <v>4.63</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N14">
         <v>824969</v>
@@ -2213,7 +2207,7 @@
         <v>4.53</v>
       </c>
       <c r="AB14">
-        <v>0.9345</v>
+        <v>0.9274</v>
       </c>
       <c r="AC14" t="s">
         <v>49</v>
@@ -2231,7 +2225,7 @@
         <v>0.218</v>
       </c>
       <c r="AH14">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI14">
         <v>0.9863</v>
@@ -2254,7 +2248,7 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2266,7 +2260,7 @@
         <v>-132</v>
       </c>
       <c r="F15">
-        <v>3.47</v>
+        <v>3.36</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2275,19 +2269,19 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>3.47</v>
+        <v>3.36</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N15">
         <v>824969</v>
       </c>
       <c r="O15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P15">
         <v>4.4</v>
@@ -2326,16 +2320,16 @@
         <v>4.6</v>
       </c>
       <c r="AB15">
-        <v>0.8197</v>
+        <v>0.8052</v>
       </c>
       <c r="AC15" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AD15">
-        <v>0.1809</v>
+        <v>0.1791</v>
       </c>
       <c r="AE15">
-        <v>0.1778</v>
+        <v>0.1934</v>
       </c>
       <c r="AF15">
         <v>9</v>
@@ -2344,19 +2338,19 @@
         <v>0.1829</v>
       </c>
       <c r="AH15">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI15">
-        <v>0.8918</v>
+        <v>0.88</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AL15" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2367,7 +2361,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>5.5</v>
@@ -2379,7 +2373,7 @@
         <v>-115</v>
       </c>
       <c r="F16">
-        <v>4.87</v>
+        <v>4.83</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2388,13 +2382,13 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.87</v>
+        <v>4.83</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N16">
         <v>823265</v>
@@ -2439,7 +2433,7 @@
         <v>3.84</v>
       </c>
       <c r="AB16">
-        <v>0.7959</v>
+        <v>0.7898</v>
       </c>
       <c r="AC16" t="s">
         <v>49</v>
@@ -2457,7 +2451,7 @@
         <v>0.2194</v>
       </c>
       <c r="AH16">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI16">
         <v>0.9963</v>
@@ -2480,7 +2474,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2492,7 +2486,7 @@
         <v>123</v>
       </c>
       <c r="F17">
-        <v>4.72</v>
+        <v>4.95</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2501,13 +2495,13 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>4.72</v>
+        <v>4.95</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N17">
         <v>823265</v>
@@ -2552,16 +2546,16 @@
         <v>4.03</v>
       </c>
       <c r="AB17">
-        <v>1.0528</v>
+        <v>1.0616</v>
       </c>
       <c r="AC17" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AD17">
-        <v>0.2324</v>
+        <v>0.2361</v>
       </c>
       <c r="AE17">
-        <v>0.2343</v>
+        <v>0.2354</v>
       </c>
       <c r="AF17">
         <v>9</v>
@@ -2570,19 +2564,19 @@
         <v>0.2137</v>
       </c>
       <c r="AH17">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI17">
-        <v>0.9959</v>
+        <v>1.0344</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AL17" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2593,7 +2587,7 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18">
         <v>3.5</v>
@@ -2605,7 +2599,7 @@
         <v>110</v>
       </c>
       <c r="F18">
-        <v>3.17</v>
+        <v>3.66</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2614,13 +2608,13 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>3.17</v>
+        <v>3.66</v>
       </c>
       <c r="L18" t="s">
         <v>46</v>
       </c>
       <c r="M18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N18">
         <v>823189</v>
@@ -2665,16 +2659,16 @@
         <v>4.06</v>
       </c>
       <c r="AB18">
-        <v>0.8261</v>
+        <v>0.9308</v>
       </c>
       <c r="AC18" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AD18">
-        <v>0.1823</v>
+        <v>0.207</v>
       </c>
       <c r="AE18">
-        <v>0.1944</v>
+        <v>0.1974</v>
       </c>
       <c r="AF18">
         <v>9</v>
@@ -2683,19 +2677,19 @@
         <v>0.2171</v>
       </c>
       <c r="AH18">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI18">
-        <v>1.0304</v>
+        <v>1.056</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AL18" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AM18">
         <v>0</v>
@@ -2706,7 +2700,7 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2718,7 +2712,7 @@
         <v>120</v>
       </c>
       <c r="F19">
-        <v>7.3</v>
+        <v>4.92</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2727,13 +2721,13 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>7.3</v>
+        <v>4.92</v>
       </c>
       <c r="L19" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N19">
         <v>823918</v>
@@ -2778,16 +2772,16 @@
         <v>4.26</v>
       </c>
       <c r="AB19">
-        <v>1.3457</v>
+        <v>0.9323</v>
       </c>
       <c r="AC19" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="AD19">
-        <v>0.297</v>
+        <v>0.2074</v>
       </c>
       <c r="AE19">
-        <v>0.2256</v>
+        <v>0.2157</v>
       </c>
       <c r="AF19">
         <v>9</v>
@@ -2796,19 +2790,19 @@
         <v>0.2004</v>
       </c>
       <c r="AH19">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI19">
-        <v>0.9913</v>
+        <v>0.9628</v>
       </c>
       <c r="AJ19" t="b">
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AL19" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AM19">
         <v>0</v>
@@ -2819,7 +2813,7 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>7.5</v>
@@ -2831,7 +2825,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>5.55</v>
+        <v>5.51</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2840,13 +2834,13 @@
         <v>45</v>
       </c>
       <c r="K20">
-        <v>5.55</v>
+        <v>5.51</v>
       </c>
       <c r="L20" t="s">
         <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N20">
         <v>823918</v>
@@ -2891,7 +2885,7 @@
         <v>3.88</v>
       </c>
       <c r="AB20">
-        <v>0.8306</v>
+        <v>0.8243</v>
       </c>
       <c r="AC20" t="s">
         <v>49</v>
@@ -2909,7 +2903,7 @@
         <v>0.2091</v>
       </c>
       <c r="AH20">
-        <v>0.2207</v>
+        <v>0.2224</v>
       </c>
       <c r="AI20">
         <v>0.9259</v>
@@ -2932,7 +2926,7 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>3.5</v>
@@ -2953,7 +2947,7 @@
         <v>45</v>
       </c>
       <c r="M21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N21" t="s">
         <v>45</v>

--- a/data/k-props/2026-08-10.xlsx
+++ b/data/k-props/2026-08-10.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="86">
   <si>
     <t>date</t>
   </si>
@@ -148,6 +148,9 @@
     <t>Sonny Gray</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -172,6 +175,12 @@
     <t>Christian Scott</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
     <t>6-7</t>
   </si>
   <si>
@@ -179,6 +188,9 @@
   </si>
   <si>
     <t>Bryce Elder</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
   <si>
     <t>Trevor Rogers</t>
@@ -793,26 +805,32 @@
       <c r="F2">
         <v>4.5</v>
       </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
       <c r="H2" t="s">
         <v>45</v>
       </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K2">
         <v>4.5</v>
       </c>
       <c r="L2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N2">
         <v>822780</v>
       </c>
       <c r="O2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P2">
         <v>5.7</v>
@@ -854,7 +872,7 @@
         <v>0.9895</v>
       </c>
       <c r="AC2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD2">
         <v>0.2201</v>
@@ -878,13 +896,25 @@
         <v>1</v>
       </c>
       <c r="AK2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>-0.5</v>
+      </c>
+      <c r="AO2">
+        <v>0.5</v>
+      </c>
+      <c r="AP2">
+        <v>-0.5</v>
+      </c>
+      <c r="AQ2">
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
@@ -892,7 +922,7 @@
         <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3">
         <v>4.5</v>
@@ -906,26 +936,32 @@
       <c r="F3">
         <v>4.17</v>
       </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
       <c r="H3" t="s">
         <v>45</v>
       </c>
+      <c r="I3">
+        <v>-0.33</v>
+      </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K3">
         <v>4.17</v>
       </c>
       <c r="L3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N3">
         <v>822780</v>
       </c>
       <c r="O3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P3">
         <v>5</v>
@@ -967,7 +1003,7 @@
         <v>0.8849</v>
       </c>
       <c r="AC3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD3">
         <v>0.1968</v>
@@ -991,13 +1027,25 @@
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>-1.17</v>
+      </c>
+      <c r="AO3">
+        <v>1.17</v>
+      </c>
+      <c r="AP3">
+        <v>-1.17</v>
+      </c>
+      <c r="AQ3">
+        <v>1.17</v>
       </c>
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
@@ -1005,7 +1053,7 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4">
         <v>5.5</v>
@@ -1019,26 +1067,32 @@
       <c r="F4">
         <v>6.61</v>
       </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I4">
+        <v>1.11</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K4">
         <v>6.61</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N4">
         <v>824887</v>
       </c>
       <c r="O4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P4">
         <v>4.6</v>
@@ -1080,7 +1134,7 @@
         <v>1.0853</v>
       </c>
       <c r="AC4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD4">
         <v>0.2414</v>
@@ -1104,13 +1158,25 @@
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>-0.61</v>
+      </c>
+      <c r="AO4">
+        <v>0.61</v>
+      </c>
+      <c r="AP4">
+        <v>-0.61</v>
+      </c>
+      <c r="AQ4">
+        <v>0.61</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
@@ -1118,7 +1184,7 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1132,26 +1198,32 @@
       <c r="F5">
         <v>5.24</v>
       </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
       <c r="H5" t="s">
         <v>45</v>
       </c>
+      <c r="I5">
+        <v>0.74</v>
+      </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="K5">
         <v>5.24</v>
       </c>
       <c r="L5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N5">
         <v>824887</v>
       </c>
       <c r="O5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P5">
         <v>5.8</v>
@@ -1193,7 +1265,7 @@
         <v>1.1602</v>
       </c>
       <c r="AC5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD5">
         <v>0.258</v>
@@ -1217,13 +1289,25 @@
         <v>1</v>
       </c>
       <c r="AK5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>-1.24</v>
+      </c>
+      <c r="AO5">
+        <v>1.24</v>
+      </c>
+      <c r="AP5">
+        <v>-1.24</v>
+      </c>
+      <c r="AQ5">
+        <v>1.24</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
@@ -1231,7 +1315,7 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1245,26 +1329,32 @@
       <c r="F6">
         <v>3.88</v>
       </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
       <c r="H6" t="s">
         <v>45</v>
       </c>
+      <c r="I6">
+        <v>-0.62</v>
+      </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K6">
         <v>3.88</v>
       </c>
       <c r="L6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N6">
         <v>823675</v>
       </c>
       <c r="O6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P6">
         <v>5.5</v>
@@ -1306,7 +1396,7 @@
         <v>0.8374</v>
       </c>
       <c r="AC6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD6">
         <v>0.1862</v>
@@ -1330,13 +1420,25 @@
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0.12</v>
+      </c>
+      <c r="AO6">
+        <v>0.12</v>
+      </c>
+      <c r="AP6">
+        <v>0.12</v>
+      </c>
+      <c r="AQ6">
+        <v>0.12</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
@@ -1344,7 +1446,7 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C7">
         <v>5.5</v>
@@ -1358,26 +1460,32 @@
       <c r="F7">
         <v>6.3</v>
       </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I7">
+        <v>0.8</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K7">
         <v>6.3</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N7">
         <v>823675</v>
       </c>
       <c r="O7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P7">
         <v>5.1</v>
@@ -1419,7 +1527,7 @@
         <v>1.2887</v>
       </c>
       <c r="AC7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD7">
         <v>0.2866</v>
@@ -1443,13 +1551,25 @@
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM7">
         <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0.7</v>
+      </c>
+      <c r="AO7">
+        <v>0.7</v>
+      </c>
+      <c r="AP7">
+        <v>0.7</v>
+      </c>
+      <c r="AQ7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
@@ -1457,7 +1577,7 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1471,26 +1591,32 @@
       <c r="F8">
         <v>3.41</v>
       </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I8">
+        <v>-0.09</v>
       </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K8">
         <v>3.41</v>
       </c>
       <c r="L8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N8">
         <v>823018</v>
       </c>
       <c r="O8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P8">
         <v>4.6</v>
@@ -1532,7 +1658,7 @@
         <v>0.9378</v>
       </c>
       <c r="AC8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD8">
         <v>0.2086</v>
@@ -1556,13 +1682,25 @@
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM8">
         <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>2.59</v>
+      </c>
+      <c r="AO8">
+        <v>2.59</v>
+      </c>
+      <c r="AP8">
+        <v>2.59</v>
+      </c>
+      <c r="AQ8">
+        <v>2.59</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
@@ -1570,7 +1708,7 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -1584,26 +1722,32 @@
       <c r="F9">
         <v>4.36</v>
       </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I9">
+        <v>0.86</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K9">
         <v>4.36</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N9">
         <v>823018</v>
       </c>
       <c r="O9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P9">
         <v>5.2</v>
@@ -1645,7 +1789,7 @@
         <v>0.998</v>
       </c>
       <c r="AC9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD9">
         <v>0.222</v>
@@ -1669,13 +1813,25 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM9">
         <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>1.64</v>
+      </c>
+      <c r="AO9">
+        <v>1.64</v>
+      </c>
+      <c r="AP9">
+        <v>1.64</v>
+      </c>
+      <c r="AQ9">
+        <v>1.64</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
@@ -1683,7 +1839,7 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C10">
         <v>6.5</v>
@@ -1697,26 +1853,32 @@
       <c r="F10">
         <v>7.66</v>
       </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I10">
+        <v>1.16</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K10">
         <v>7.66</v>
       </c>
       <c r="L10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N10">
         <v>823998</v>
       </c>
       <c r="O10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P10">
         <v>5.4</v>
@@ -1758,7 +1920,7 @@
         <v>1.2845</v>
       </c>
       <c r="AC10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD10">
         <v>0.2857</v>
@@ -1782,13 +1944,25 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM10">
         <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>1.34</v>
+      </c>
+      <c r="AO10">
+        <v>1.34</v>
+      </c>
+      <c r="AP10">
+        <v>1.34</v>
+      </c>
+      <c r="AQ10">
+        <v>1.34</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
@@ -1796,7 +1970,7 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C11">
         <v>6.5</v>
@@ -1810,26 +1984,32 @@
       <c r="F11">
         <v>10.01</v>
       </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
       <c r="H11" t="s">
         <v>45</v>
       </c>
+      <c r="I11">
+        <v>3.51</v>
+      </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="K11">
         <v>10.01</v>
       </c>
       <c r="L11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N11">
         <v>823998</v>
       </c>
       <c r="O11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P11">
         <v>5.6</v>
@@ -1871,7 +2051,7 @@
         <v>1.3326</v>
       </c>
       <c r="AC11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD11">
         <v>0.2964</v>
@@ -1895,13 +2075,25 @@
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM11">
         <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>-4.01</v>
+      </c>
+      <c r="AO11">
+        <v>4.01</v>
+      </c>
+      <c r="AP11">
+        <v>-4.01</v>
+      </c>
+      <c r="AQ11">
+        <v>4.01</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
@@ -1909,7 +2101,7 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C12">
         <v>3.5</v>
@@ -1923,26 +2115,32 @@
       <c r="F12">
         <v>3.98</v>
       </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
       <c r="H12" t="s">
         <v>45</v>
       </c>
+      <c r="I12">
+        <v>0.48</v>
+      </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K12">
         <v>3.98</v>
       </c>
       <c r="L12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N12">
         <v>825048</v>
       </c>
       <c r="O12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P12">
         <v>5.3</v>
@@ -1984,7 +2182,7 @@
         <v>0.8806</v>
       </c>
       <c r="AC12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD12">
         <v>0.1959</v>
@@ -2008,13 +2206,25 @@
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM12">
         <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>-0.98</v>
+      </c>
+      <c r="AO12">
+        <v>0.98</v>
+      </c>
+      <c r="AP12">
+        <v>-0.98</v>
+      </c>
+      <c r="AQ12">
+        <v>0.98</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
@@ -2022,7 +2232,7 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -2036,26 +2246,32 @@
       <c r="F13">
         <v>5.37</v>
       </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
       <c r="H13" t="s">
         <v>45</v>
       </c>
+      <c r="I13">
+        <v>0.87</v>
+      </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="K13">
         <v>5.37</v>
       </c>
       <c r="L13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N13">
         <v>825048</v>
       </c>
       <c r="O13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P13">
         <v>5.5</v>
@@ -2097,7 +2313,7 @@
         <v>1.0394</v>
       </c>
       <c r="AC13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD13">
         <v>0.2312</v>
@@ -2121,13 +2337,25 @@
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM13">
         <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>-1.37</v>
+      </c>
+      <c r="AO13">
+        <v>1.37</v>
+      </c>
+      <c r="AP13">
+        <v>-1.37</v>
+      </c>
+      <c r="AQ13">
+        <v>1.37</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
@@ -2135,7 +2363,7 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C14">
         <v>4.5</v>
@@ -2149,26 +2377,32 @@
       <c r="F14">
         <v>4.63</v>
       </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
       <c r="H14" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I14">
+        <v>0.13</v>
       </c>
       <c r="J14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K14">
         <v>4.63</v>
       </c>
       <c r="L14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N14">
         <v>824969</v>
       </c>
       <c r="O14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P14">
         <v>5.1</v>
@@ -2210,7 +2444,7 @@
         <v>0.9274</v>
       </c>
       <c r="AC14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD14">
         <v>0.2063</v>
@@ -2234,13 +2468,25 @@
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM14">
         <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0.37</v>
+      </c>
+      <c r="AO14">
+        <v>0.37</v>
+      </c>
+      <c r="AP14">
+        <v>0.37</v>
+      </c>
+      <c r="AQ14">
+        <v>0.37</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
@@ -2248,7 +2494,7 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2262,26 +2508,32 @@
       <c r="F15">
         <v>3.36</v>
       </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
       <c r="H15" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I15">
+        <v>-1.14</v>
       </c>
       <c r="J15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="K15">
         <v>3.36</v>
       </c>
       <c r="L15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N15">
         <v>824969</v>
       </c>
       <c r="O15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P15">
         <v>4.4</v>
@@ -2323,7 +2575,7 @@
         <v>0.8052</v>
       </c>
       <c r="AC15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD15">
         <v>0.1791</v>
@@ -2347,13 +2599,25 @@
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM15">
         <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>1.64</v>
+      </c>
+      <c r="AO15">
+        <v>1.64</v>
+      </c>
+      <c r="AP15">
+        <v>1.64</v>
+      </c>
+      <c r="AQ15">
+        <v>1.64</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
@@ -2361,7 +2625,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C16">
         <v>5.5</v>
@@ -2375,26 +2639,32 @@
       <c r="F16">
         <v>4.83</v>
       </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
       <c r="H16" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I16">
+        <v>-0.67</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K16">
         <v>4.83</v>
       </c>
       <c r="L16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N16">
         <v>823265</v>
       </c>
       <c r="O16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P16">
         <v>5</v>
@@ -2436,7 +2706,7 @@
         <v>0.7898</v>
       </c>
       <c r="AC16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD16">
         <v>0.1757</v>
@@ -2460,13 +2730,25 @@
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM16">
         <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>2.17</v>
+      </c>
+      <c r="AO16">
+        <v>2.17</v>
+      </c>
+      <c r="AP16">
+        <v>2.17</v>
+      </c>
+      <c r="AQ16">
+        <v>2.17</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
@@ -2474,7 +2756,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2488,26 +2770,32 @@
       <c r="F17">
         <v>4.95</v>
       </c>
+      <c r="G17">
+        <v>6</v>
+      </c>
       <c r="H17" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I17">
+        <v>0.45</v>
       </c>
       <c r="J17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K17">
         <v>4.95</v>
       </c>
       <c r="L17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N17">
         <v>823265</v>
       </c>
       <c r="O17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P17">
         <v>5.3</v>
@@ -2549,7 +2837,7 @@
         <v>1.0616</v>
       </c>
       <c r="AC17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD17">
         <v>0.2361</v>
@@ -2573,13 +2861,25 @@
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM17">
         <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>1.05</v>
+      </c>
+      <c r="AO17">
+        <v>1.05</v>
+      </c>
+      <c r="AP17">
+        <v>1.05</v>
+      </c>
+      <c r="AQ17">
+        <v>1.05</v>
       </c>
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
@@ -2587,7 +2887,7 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C18">
         <v>3.5</v>
@@ -2601,26 +2901,32 @@
       <c r="F18">
         <v>3.66</v>
       </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
       <c r="H18" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="I18">
+        <v>0.16</v>
       </c>
       <c r="J18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K18">
         <v>3.66</v>
       </c>
       <c r="L18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N18">
         <v>823189</v>
       </c>
       <c r="O18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2662,7 +2968,7 @@
         <v>0.9308</v>
       </c>
       <c r="AC18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD18">
         <v>0.207</v>
@@ -2686,13 +2992,25 @@
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM18">
         <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>2.34</v>
+      </c>
+      <c r="AO18">
+        <v>2.34</v>
+      </c>
+      <c r="AP18">
+        <v>2.34</v>
+      </c>
+      <c r="AQ18">
+        <v>2.34</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
@@ -2700,7 +3018,7 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2714,26 +3032,32 @@
       <c r="F19">
         <v>4.92</v>
       </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
       <c r="H19" t="s">
         <v>45</v>
       </c>
+      <c r="I19">
+        <v>0.42</v>
+      </c>
       <c r="J19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K19">
         <v>4.92</v>
       </c>
       <c r="L19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M19" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="N19">
         <v>823918</v>
       </c>
       <c r="O19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P19">
         <v>5.6</v>
@@ -2775,7 +3099,7 @@
         <v>0.9323</v>
       </c>
       <c r="AC19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD19">
         <v>0.2074</v>
@@ -2799,13 +3123,25 @@
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM19">
         <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>-2.92</v>
+      </c>
+      <c r="AO19">
+        <v>2.92</v>
+      </c>
+      <c r="AP19">
+        <v>-2.92</v>
+      </c>
+      <c r="AQ19">
+        <v>2.92</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
@@ -2813,7 +3149,7 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C20">
         <v>7.5</v>
@@ -2827,26 +3163,32 @@
       <c r="F20">
         <v>5.51</v>
       </c>
+      <c r="G20">
+        <v>6</v>
+      </c>
       <c r="H20" t="s">
         <v>45</v>
       </c>
+      <c r="I20">
+        <v>-1.99</v>
+      </c>
       <c r="J20" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K20">
         <v>5.51</v>
       </c>
       <c r="L20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M20" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="N20">
         <v>823918</v>
       </c>
       <c r="O20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -2888,7 +3230,7 @@
         <v>0.8243</v>
       </c>
       <c r="AC20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD20">
         <v>0.1833</v>
@@ -2912,13 +3254,25 @@
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AL20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM20">
         <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0.49</v>
+      </c>
+      <c r="AO20">
+        <v>0.49</v>
+      </c>
+      <c r="AP20">
+        <v>0.49</v>
+      </c>
+      <c r="AQ20">
+        <v>0.49</v>
       </c>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.25">
@@ -2926,7 +3280,7 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C21">
         <v>3.5</v>
@@ -2937,38 +3291,41 @@
       <c r="E21">
         <v>134</v>
       </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
       <c r="H21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="J21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S21">
         <v>6</v>
       </c>
       <c r="AC21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AL21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
